--- a/examples/dlux/02_act_dlux.xlsx
+++ b/examples/dlux/02_act_dlux.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Toyota RAV4</t>
+          <t>Hyundai Solaris</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Мойка кузова и химчистка салона</t>
+          <t>Мойка кузова</t>
         </is>
       </c>
     </row>
@@ -498,12 +498,222 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Hyundai Solaris</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Мойка двигателя и полировка фар</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kia Rio</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Химчистка салона полная</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Skoda Octavia</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Шиномонтаж 4 колеса и балансировка 4 колеса</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Volkswagen Polo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Антикоррозийная обработка днища</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Toyota RAV4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Мойка кузова и химчистка салона полная</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kia Sportage</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Мойка кузова при сильном загрязнении</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mitsubishi Outlander</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Полировка кузова и полировка фар</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nissan X-Trail</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Шиномонтаж 4 колеса</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hyundai Santa Fe</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Антикоррозийная обработка днища</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Mercedes Sprinter</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Мойка кузова</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ford Transit</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Мойка кузова при сильном загрязнении и химчистка салона частичная</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Volkswagen Crafter</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Мойка двигателя и полировка кузова</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Peugeot Boxer</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Шиномонтаж 4 колеса и балансировка 4 колеса</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tesla Model S</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Мойка кузова</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BYD Han</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Полировка кузова и химчистка салона частичная</t>
         </is>
       </c>
     </row>
